--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/Hyperlink_External/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/Hyperlink_External/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rb6d77d96220e496c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rc6ad954103f14191"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -53,7 +53,7 @@
     </x:row>
   </x:sheetData>
   <x:hyperlinks>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A1" r:id="R427f5c83b30c4c42" tooltip="Open in browser" display="dotnet/Open-XML-SDK"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A1" r:id="R92376a6b817a4438" tooltip="Open in browser" display="dotnet/Open-XML-SDK"/>
   </x:hyperlinks>
 </x:worksheet>
 </file>
--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/Hyperlink_External/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/Hyperlink_External/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rc6ad954103f14191"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rd7c277d1cff4440a"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -53,7 +53,7 @@
     </x:row>
   </x:sheetData>
   <x:hyperlinks>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A1" r:id="R92376a6b817a4438" tooltip="Open in browser" display="dotnet/Open-XML-SDK"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A1" r:id="R9a83560eaec84e73" tooltip="Open in browser" display="dotnet/Open-XML-SDK"/>
   </x:hyperlinks>
 </x:worksheet>
 </file>
--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/Hyperlink_External/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/Hyperlink_External/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rd7c277d1cff4440a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Ra2bbce61d1a8430c"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -53,7 +53,7 @@
     </x:row>
   </x:sheetData>
   <x:hyperlinks>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A1" r:id="R9a83560eaec84e73" tooltip="Open in browser" display="dotnet/Open-XML-SDK"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A1" r:id="Ra0eb5078bf994ca4" tooltip="Open in browser" display="dotnet/Open-XML-SDK"/>
   </x:hyperlinks>
 </x:worksheet>
 </file>
--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/Hyperlink_External/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/Hyperlink_External/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Ra2bbce61d1a8430c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R0493f1c23e104d36"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -53,7 +53,7 @@
     </x:row>
   </x:sheetData>
   <x:hyperlinks>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A1" r:id="Ra0eb5078bf994ca4" tooltip="Open in browser" display="dotnet/Open-XML-SDK"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A1" r:id="R185ebaedff3d4f77" tooltip="Open in browser" display="dotnet/Open-XML-SDK"/>
   </x:hyperlinks>
 </x:worksheet>
 </file>
--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/Hyperlink_External/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/Hyperlink_External/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R0493f1c23e104d36"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rb2e3bb89c88b497e"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -53,7 +53,7 @@
     </x:row>
   </x:sheetData>
   <x:hyperlinks>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A1" r:id="R185ebaedff3d4f77" tooltip="Open in browser" display="dotnet/Open-XML-SDK"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A1" r:id="Re097c9d73cc0420f" tooltip="Open in browser" display="dotnet/Open-XML-SDK"/>
   </x:hyperlinks>
 </x:worksheet>
 </file>
--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/Hyperlink_External/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/Hyperlink_External/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rb2e3bb89c88b497e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R72bd4edcf9154053"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -53,7 +53,7 @@
     </x:row>
   </x:sheetData>
   <x:hyperlinks>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A1" r:id="Re097c9d73cc0420f" tooltip="Open in browser" display="dotnet/Open-XML-SDK"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A1" r:id="R18d5e3471b2745bb" tooltip="Open in browser" display="dotnet/Open-XML-SDK"/>
   </x:hyperlinks>
 </x:worksheet>
 </file>
--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/Hyperlink_External/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/Hyperlink_External/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R72bd4edcf9154053"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rf9d2e5ccde6d49cb"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -53,7 +53,7 @@
     </x:row>
   </x:sheetData>
   <x:hyperlinks>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A1" r:id="R18d5e3471b2745bb" tooltip="Open in browser" display="dotnet/Open-XML-SDK"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A1" r:id="R32ab7acacfee4833" tooltip="Open in browser" display="dotnet/Open-XML-SDK"/>
   </x:hyperlinks>
 </x:worksheet>
 </file>
--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/Hyperlink_External/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/Hyperlink_External/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rf9d2e5ccde6d49cb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R486304b4260c43d4"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -53,7 +53,7 @@
     </x:row>
   </x:sheetData>
   <x:hyperlinks>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A1" r:id="R32ab7acacfee4833" tooltip="Open in browser" display="dotnet/Open-XML-SDK"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A1" r:id="R43d95e0203384927" tooltip="Open in browser" display="dotnet/Open-XML-SDK"/>
   </x:hyperlinks>
 </x:worksheet>
 </file>
--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/Hyperlink_External/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/Hyperlink_External/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R486304b4260c43d4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R9f937e53c10a4db8"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -53,7 +53,7 @@
     </x:row>
   </x:sheetData>
   <x:hyperlinks>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A1" r:id="R43d95e0203384927" tooltip="Open in browser" display="dotnet/Open-XML-SDK"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A1" r:id="R10a3f4c10c3b45a7" tooltip="Open in browser" display="dotnet/Open-XML-SDK"/>
   </x:hyperlinks>
 </x:worksheet>
 </file>
--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/Hyperlink_External/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/Hyperlink_External/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R9f937e53c10a4db8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R5d1d8408b3174f22"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -53,7 +53,7 @@
     </x:row>
   </x:sheetData>
   <x:hyperlinks>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A1" r:id="R10a3f4c10c3b45a7" tooltip="Open in browser" display="dotnet/Open-XML-SDK"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A1" r:id="Reded8141df524e4b" tooltip="Open in browser" display="dotnet/Open-XML-SDK"/>
   </x:hyperlinks>
 </x:worksheet>
 </file>
--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/Hyperlink_External/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/Hyperlink_External/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R5d1d8408b3174f22"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R1a9265bd35cc490a"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -53,7 +53,7 @@
     </x:row>
   </x:sheetData>
   <x:hyperlinks>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A1" r:id="Reded8141df524e4b" tooltip="Open in browser" display="dotnet/Open-XML-SDK"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A1" r:id="Reb90ce0009ab4072" tooltip="Open in browser" display="dotnet/Open-XML-SDK"/>
   </x:hyperlinks>
 </x:worksheet>
 </file>
--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/Hyperlink_External/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/Hyperlink_External/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R1a9265bd35cc490a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R5436892b41bf4544"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -53,7 +53,7 @@
     </x:row>
   </x:sheetData>
   <x:hyperlinks>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A1" r:id="Reb90ce0009ab4072" tooltip="Open in browser" display="dotnet/Open-XML-SDK"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A1" r:id="R538517637b2d47e0" tooltip="Open in browser" display="dotnet/Open-XML-SDK"/>
   </x:hyperlinks>
 </x:worksheet>
 </file>
--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/Hyperlink_External/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/Hyperlink_External/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R5436892b41bf4544"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R72217121d90a48d7"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -53,7 +53,7 @@
     </x:row>
   </x:sheetData>
   <x:hyperlinks>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A1" r:id="R538517637b2d47e0" tooltip="Open in browser" display="dotnet/Open-XML-SDK"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A1" r:id="R0f48e46d14fb4b7e" tooltip="Open in browser" display="dotnet/Open-XML-SDK"/>
   </x:hyperlinks>
 </x:worksheet>
 </file>
--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/Hyperlink_External/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/Hyperlink_External/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R72217121d90a48d7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Ra0ffa9c3966148f5"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -53,7 +53,7 @@
     </x:row>
   </x:sheetData>
   <x:hyperlinks>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A1" r:id="R0f48e46d14fb4b7e" tooltip="Open in browser" display="dotnet/Open-XML-SDK"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A1" r:id="R3c7d7c2bfe204203" tooltip="Open in browser" display="dotnet/Open-XML-SDK"/>
   </x:hyperlinks>
 </x:worksheet>
 </file>
--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/Hyperlink_External/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/Hyperlink_External/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Ra0ffa9c3966148f5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R53435aeb38464798"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -53,7 +53,7 @@
     </x:row>
   </x:sheetData>
   <x:hyperlinks>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A1" r:id="R3c7d7c2bfe204203" tooltip="Open in browser" display="dotnet/Open-XML-SDK"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A1" r:id="R27c49fc1952a43df" tooltip="Open in browser" display="dotnet/Open-XML-SDK"/>
   </x:hyperlinks>
 </x:worksheet>
 </file>